--- a/data/transacciones_junio.xlsx
+++ b/data/transacciones_junio.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,43 +417,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="B2:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">REGISTRO DE TRANSACCIONES (JUNIO 2026-1) </t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>Responsable(s) de la actualización</t>
+          <t>Responsable(s) de la actualizacion</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Última actualización</t>
+          <t>Ultima actualizacion</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lesly Guzmán</t>
+          <t>Amanda Gomez</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
@@ -468,57 +469,57 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Ord.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>Fecha de registro</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>Nombre de la Actividad</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Glosa</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Monto (S/.)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>Descripcion</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>Fecha del Comprobante</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>Tipo de Comprobante</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Codigo de Comprobante (N°, Serie, etc.)</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Nombre / Razón Social</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Codigo de Comprobante</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>Nombre / Razon Social</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>RUC / DNI</t>
         </is>
@@ -529,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1049.5</v>
+        <v>1049.45</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -543,12 +544,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Constitucion</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -557,6 +563,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>Reserva de nombre</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yape Franco Raf</t>
         </is>
       </c>
     </row>
@@ -566,20 +577,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Constitucion</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>130</v>
+        <v>821.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Costos registrales</t>
+          <t>Costos notariales</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TRANSF.BCO.BBVA</t>
         </is>
       </c>
     </row>
@@ -589,20 +610,558 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Constitucion</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Gasto</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>821.5</v>
+        <v>130</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Costos notariales</t>
+          <t>Costos registrales</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>TRANSF.BCO.BBVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Venta de tickets de rifa</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>TRANSF.BCO.BANBIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Venta de tickets de rifa</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yape Fabiana Val</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Venta de tickets de rifa</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yape Yanely Mog</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Venta de tickets de rifa</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Yape Elvis Per</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Venta de tickets de rifa</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Yape Valeria Ing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Venta de ticket de rifa</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Yape Oscar Gar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Venta de ticket de rifa</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Yape Axel Cam</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Venta de tickets de rifa</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yape Alonzo Gon</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pre 180 Talks</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Catering para evento Pre 180 Talks</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yape Diego Cor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pre 180 Talks</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Regalos para jueces Pre 180 Talks</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Yape Mariana Veg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Integracion</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Materiales integracion picnic</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Yape Mariana Veg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pre 180 Talks</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vasos y bocaditos Pre 180 Talks</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Yape Maria Par</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Conexion 180 DC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Taller Conexion 180 DC (entrada S/ 5)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Yape Brian Ber</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>17</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Venta de tickets de rifa</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yape Brian Ber</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>18</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Conexion 180 DC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Taller Conexion 180 DC (entrada S/ 5)</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yape Luciana Baq</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>19</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Rifa pro fondos</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Venta de ticket de rifa</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Yape Sayda Mac</t>
         </is>
       </c>
     </row>
